--- a/products/Catering_Business_Manager_PREMIUM_Classic_EXAMPLE.xlsx
+++ b/products/Catering_Business_Manager_PREMIUM_Classic_EXAMPLE.xlsx
@@ -6857,13 +6857,13 @@
                   <c:v>Bilal Traders</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v/>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -7891,11 +7891,11 @@
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=1)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=1)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J2" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=1)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=1)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K2" s="1">
@@ -7938,11 +7938,11 @@
         <v>2</v>
       </c>
       <c r="I3" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=2)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=2)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J3" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=2)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=2)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K3" s="1">
@@ -7985,11 +7985,11 @@
         <v>3</v>
       </c>
       <c r="I4" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=3)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=3)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J4" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=3)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=3)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K4" s="1">
@@ -8032,11 +8032,11 @@
         <v>4</v>
       </c>
       <c r="I5" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=4)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=4)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J5" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=4)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=4)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K5" s="1">
@@ -8079,11 +8079,11 @@
         <v>5</v>
       </c>
       <c r="I6" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=5)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=5)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J6" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=5)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=5)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K6" s="1">
@@ -8126,11 +8126,11 @@
         <v>6</v>
       </c>
       <c r="I7" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=6)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=6)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=6)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=6)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K7" s="1">
@@ -8173,11 +8173,11 @@
         <v>7</v>
       </c>
       <c r="I8" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=7)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=7)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=7)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=7)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K8" s="1">
@@ -8220,11 +8220,11 @@
         <v>8</v>
       </c>
       <c r="I9" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=8)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=8)),'💰 Payments'!$J$8:$J$67)</f>
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=8)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=8)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>1910.0</v>
       </c>
       <c r="K9" s="1">
@@ -8267,11 +8267,11 @@
         <v>9</v>
       </c>
       <c r="I10" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=9)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=9)),'💰 Payments'!$J$8:$J$67)</f>
         <v>11010</v>
       </c>
       <c r="J10" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=9)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=9)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>8368.0</v>
       </c>
       <c r="K10" s="1">
@@ -8314,11 +8314,11 @@
         <v>10</v>
       </c>
       <c r="I11" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=10)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=10)),'💰 Payments'!$J$8:$J$67)</f>
         <v>6720</v>
       </c>
       <c r="J11" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=10)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=10)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K11" s="1">
@@ -8361,11 +8361,11 @@
         <v>11</v>
       </c>
       <c r="I12" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=11)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=11)),'💰 Payments'!$J$8:$J$67)</f>
         <v>2840</v>
       </c>
       <c r="J12" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=11)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=11)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K12" s="1">
@@ -8408,11 +8408,11 @@
         <v>12</v>
       </c>
       <c r="I13" s="1">
-        <f>SUMPRODUCT(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=12)*'💰 Payments'!$J$8:$J$67)</f>
+        <f>SUMPRODUCT(--(('💰 Payments'!$E$8:$E$67&lt;&gt;"")*(MONTH('💰 Payments'!$E$8:$E$67)=12)),'💰 Payments'!$J$8:$J$67)</f>
         <v>3560</v>
       </c>
       <c r="J13" s="1">
-        <f>SUMPRODUCT(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=12)*'💸 Expenses'!$G$8:$G$67)</f>
+        <f>SUMPRODUCT(--(('💸 Expenses'!$C$8:$C$67&lt;&gt;"")*(MONTH('💸 Expenses'!$C$8:$C$67)=12)),'💸 Expenses'!$G$8:$G$67)</f>
         <v>0</v>
       </c>
       <c r="K13" s="1">
@@ -8739,7 +8739,7 @@
         <v>82</v>
       </c>
       <c r="AF24" s="1">
-        <f>SUMPRODUCT(('🛒 Shopping List'!$G$8:$G$47&gt;0)*('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓"))</f>
+        <f>SUMPRODUCT(ISNUMBER('🛒 Shopping List'!$G$8:$G$47)*('🛒 Shopping List'!$G$8:$G$47&gt;0)*('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓"))</f>
         <v>2</v>
       </c>
     </row>
@@ -8772,7 +8772,7 @@
         <v>83</v>
       </c>
       <c r="AF25" s="1">
-        <f>SUMPRODUCT(('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓")*('🛒 Shopping List'!$G$8:$G$47&gt;0)*'🛒 Shopping List'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(ISNUMBER('🛒 Shopping List'!$G$8:$G$47)*('🛒 Shopping List'!$G$8:$G$47&gt;0)*('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓"),'🛒 Shopping List'!$I$8:$I$47)</f>
         <v>268.0</v>
       </c>
     </row>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="U30" s="1">
         <f>IF($T30="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T30,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA30" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),29),"")</f>
@@ -9209,7 +9209,7 @@
       </c>
       <c r="U36" s="1">
         <f>IF($T36="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T36,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA36" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),35),"")</f>
@@ -9264,11 +9264,11 @@
     <row r="38" spans="14:32">
       <c r="Q38" s="1">
         <f>IF('👥 Clients'!$C$20="","",'👥 Clients'!$C$20)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R38" s="1">
         <f>IF($Q38="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q38,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T38" s="1" t="str">
         <f>IF('🍽️ Menu Costing'!$C$20="","",'🍽️ Menu Costing'!$C$20)</f>
@@ -9294,11 +9294,11 @@
     <row r="39" spans="14:32">
       <c r="Q39" s="1">
         <f>IF('👥 Clients'!$C$21="","",'👥 Clients'!$C$21)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R39" s="1">
         <f>IF($Q39="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q39,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T39" s="1" t="str">
         <f>IF('🍽️ Menu Costing'!$C$21="","",'🍽️ Menu Costing'!$C$21)</f>
@@ -9324,19 +9324,19 @@
     <row r="40" spans="14:32">
       <c r="Q40" s="1">
         <f>IF('👥 Clients'!$C$22="","",'👥 Clients'!$C$22)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="R40" s="1">
         <f>IF($Q40="","",SUMIF('💰 Payments'!$D$8:$D$67,$Q40,'💰 Payments'!$J$8:$J$67))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="T40" s="1">
         <f>IF('🍽️ Menu Costing'!$C$22="","",'🍽️ Menu Costing'!$C$22)</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="U40" s="1">
         <f>IF($T40="","",SUMPRODUCT(('📅 Events'!$H$8:$H$47&lt;&gt;"")*IFERROR(--ISNUMBER(SEARCH($T40,'📅 Events'!$H$8:$H$47)),0)))</f>
-        <v>0</v>
+        <v/>
       </c>
       <c r="AA40" s="1">
         <f>IFERROR(AGGREGATE(15,6,'📅 Events'!$E$8:$E$47/('📅 Events'!$E$8:$E$47&gt;=TODAY())*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"🎉 Completed"),39),"")</f>
@@ -9364,7 +9364,7 @@
     </row>
     <row r="42" spans="14:32">
       <c r="AA42" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),1),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),1),"")</f>
         <v>46275.0</v>
       </c>
       <c r="AB42" s="1" t="str">
@@ -9378,7 +9378,7 @@
     </row>
     <row r="43" spans="14:32">
       <c r="AA43" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),2),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),2),"")</f>
         <v>46284.0</v>
       </c>
       <c r="AB43" s="1" t="str">
@@ -9392,7 +9392,7 @@
     </row>
     <row r="44" spans="14:32">
       <c r="AA44" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),3),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),3),"")</f>
         <v>46298.0</v>
       </c>
       <c r="AB44" s="1" t="str">
@@ -9406,7 +9406,7 @@
     </row>
     <row r="45" spans="14:32">
       <c r="AA45" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),4),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),4),"")</f>
         <v>46305.0</v>
       </c>
       <c r="AB45" s="1" t="str">
@@ -9420,7 +9420,7 @@
     </row>
     <row r="46" spans="14:32">
       <c r="AA46" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),5),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),5),"")</f>
         <v>46312.0</v>
       </c>
       <c r="AB46" s="1" t="str">
@@ -9434,7 +9434,7 @@
     </row>
     <row r="47" spans="14:32">
       <c r="AA47" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),6),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),6),"")</f>
         <v>46319.0</v>
       </c>
       <c r="AB47" s="1" t="str">
@@ -9448,7 +9448,7 @@
     </row>
     <row r="48" spans="14:32">
       <c r="AA48" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),7),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),7),"")</f>
         <v>46333.0</v>
       </c>
       <c r="AB48" s="1" t="str">
@@ -9462,7 +9462,7 @@
     </row>
     <row r="49" spans="27:29">
       <c r="AA49" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),8),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),8),"")</f>
         <v>46340.0</v>
       </c>
       <c r="AB49" s="1" t="str">
@@ -9476,7 +9476,7 @@
     </row>
     <row r="50" spans="27:29">
       <c r="AA50" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),9),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),9),"")</f>
         <v>46347.0</v>
       </c>
       <c r="AB50" s="1" t="str">
@@ -9490,7 +9490,7 @@
     </row>
     <row r="51" spans="27:29">
       <c r="AA51" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),10),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),10),"")</f>
         <v>46361.0</v>
       </c>
       <c r="AB51" s="1" t="str">
@@ -9504,7 +9504,7 @@
     </row>
     <row r="52" spans="27:29">
       <c r="AA52" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),11),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),11),"")</f>
         <v>46375.0</v>
       </c>
       <c r="AB52" s="1" t="str">
@@ -9518,7 +9518,7 @@
     </row>
     <row r="53" spans="27:29">
       <c r="AA53" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),12),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),12),"")</f>
         <v/>
       </c>
       <c r="AB53" s="1">
@@ -9527,12 +9527,12 @@
       </c>
       <c r="AC53" s="1">
         <f>IF($AA53="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA53,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="54" spans="27:29">
       <c r="AA54" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),13),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),13),"")</f>
         <v/>
       </c>
       <c r="AB54" s="1">
@@ -9541,12 +9541,12 @@
       </c>
       <c r="AC54" s="1">
         <f>IF($AA54="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA54,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="27:29">
       <c r="AA55" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),14),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),14),"")</f>
         <v/>
       </c>
       <c r="AB55" s="1">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="AC55" s="1">
         <f>IF($AA55="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA55,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="56" spans="27:29">
       <c r="AA56" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),15),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),15),"")</f>
         <v/>
       </c>
       <c r="AB56" s="1">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="AC56" s="1">
         <f>IF($AA56="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA56,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="57" spans="27:29">
       <c r="AA57" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),16),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),16),"")</f>
         <v/>
       </c>
       <c r="AB57" s="1">
@@ -9583,12 +9583,12 @@
       </c>
       <c r="AC57" s="1">
         <f>IF($AA57="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA57,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="58" spans="27:29">
       <c r="AA58" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),17),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),17),"")</f>
         <v/>
       </c>
       <c r="AB58" s="1">
@@ -9597,12 +9597,12 @@
       </c>
       <c r="AC58" s="1">
         <f>IF($AA58="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA58,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="59" spans="27:29">
       <c r="AA59" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),18),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),18),"")</f>
         <v/>
       </c>
       <c r="AB59" s="1">
@@ -9611,12 +9611,12 @@
       </c>
       <c r="AC59" s="1">
         <f>IF($AA59="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA59,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="60" spans="27:29">
       <c r="AA60" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),19),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),19),"")</f>
         <v/>
       </c>
       <c r="AB60" s="1">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="AC60" s="1">
         <f>IF($AA60="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA60,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="61" spans="27:29">
       <c r="AA61" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),20),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),20),"")</f>
         <v/>
       </c>
       <c r="AB61" s="1">
@@ -9639,12 +9639,12 @@
       </c>
       <c r="AC61" s="1">
         <f>IF($AA61="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA61,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="62" spans="27:29">
       <c r="AA62" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),21),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),21),"")</f>
         <v/>
       </c>
       <c r="AB62" s="1">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="AC62" s="1">
         <f>IF($AA62="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA62,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="63" spans="27:29">
       <c r="AA63" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),22),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),22),"")</f>
         <v/>
       </c>
       <c r="AB63" s="1">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="AC63" s="1">
         <f>IF($AA63="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA63,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="64" spans="27:29">
       <c r="AA64" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),23),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),23),"")</f>
         <v/>
       </c>
       <c r="AB64" s="1">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="AC64" s="1">
         <f>IF($AA64="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA64,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="65" spans="27:29">
       <c r="AA65" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),24),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),24),"")</f>
         <v/>
       </c>
       <c r="AB65" s="1">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="AC65" s="1">
         <f>IF($AA65="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA65,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="66" spans="27:29">
       <c r="AA66" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),25),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),25),"")</f>
         <v/>
       </c>
       <c r="AB66" s="1">
@@ -9709,12 +9709,12 @@
       </c>
       <c r="AC66" s="1">
         <f>IF($AA66="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA66,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="67" spans="27:29">
       <c r="AA67" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),26),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),26),"")</f>
         <v/>
       </c>
       <c r="AB67" s="1">
@@ -9723,12 +9723,12 @@
       </c>
       <c r="AC67" s="1">
         <f>IF($AA67="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA67,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="68" spans="27:29">
       <c r="AA68" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),27),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),27),"")</f>
         <v/>
       </c>
       <c r="AB68" s="1">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="AC68" s="1">
         <f>IF($AA68="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA68,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="69" spans="27:29">
       <c r="AA69" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),28),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),28),"")</f>
         <v/>
       </c>
       <c r="AB69" s="1">
@@ -9751,12 +9751,12 @@
       </c>
       <c r="AC69" s="1">
         <f>IF($AA69="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA69,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="70" spans="27:29">
       <c r="AA70" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),29),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),29),"")</f>
         <v/>
       </c>
       <c r="AB70" s="1">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="AC70" s="1">
         <f>IF($AA70="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA70,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="71" spans="27:29">
       <c r="AA71" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),30),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),30),"")</f>
         <v/>
       </c>
       <c r="AB71" s="1">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="AC71" s="1">
         <f>IF($AA71="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA71,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="72" spans="27:29">
       <c r="AA72" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),31),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),31),"")</f>
         <v/>
       </c>
       <c r="AB72" s="1">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="AC72" s="1">
         <f>IF($AA72="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA72,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="73" spans="27:29">
       <c r="AA73" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),32),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),32),"")</f>
         <v/>
       </c>
       <c r="AB73" s="1">
@@ -9807,12 +9807,12 @@
       </c>
       <c r="AC73" s="1">
         <f>IF($AA73="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA73,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="74" spans="27:29">
       <c r="AA74" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),33),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),33),"")</f>
         <v/>
       </c>
       <c r="AB74" s="1">
@@ -9821,12 +9821,12 @@
       </c>
       <c r="AC74" s="1">
         <f>IF($AA74="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA74,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="75" spans="27:29">
       <c r="AA75" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),34),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),34),"")</f>
         <v/>
       </c>
       <c r="AB75" s="1">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="AC75" s="1">
         <f>IF($AA75="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA75,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="76" spans="27:29">
       <c r="AA76" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),35),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),35),"")</f>
         <v/>
       </c>
       <c r="AB76" s="1">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="AC76" s="1">
         <f>IF($AA76="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA76,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="77" spans="27:29">
       <c r="AA77" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),36),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),36),"")</f>
         <v/>
       </c>
       <c r="AB77" s="1">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="AC77" s="1">
         <f>IF($AA77="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA77,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="78" spans="27:29">
       <c r="AA78" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),37),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),37),"")</f>
         <v/>
       </c>
       <c r="AB78" s="1">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="AC78" s="1">
         <f>IF($AA78="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA78,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="79" spans="27:29">
       <c r="AA79" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),38),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),38),"")</f>
         <v/>
       </c>
       <c r="AB79" s="1">
@@ -9891,12 +9891,12 @@
       </c>
       <c r="AC79" s="1">
         <f>IF($AA79="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA79,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="80" spans="27:29">
       <c r="AA80" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),39),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),39),"")</f>
         <v/>
       </c>
       <c r="AB80" s="1">
@@ -9905,12 +9905,12 @@
       </c>
       <c r="AC80" s="1">
         <f>IF($AA80="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA80,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="81" spans="27:29">
       <c r="AA81" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),40),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),40),"")</f>
         <v/>
       </c>
       <c r="AB81" s="1">
@@ -9919,12 +9919,12 @@
       </c>
       <c r="AC81" s="1">
         <f>IF($AA81="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA81,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="82" spans="27:29">
       <c r="AA82" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),41),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),41),"")</f>
         <v/>
       </c>
       <c r="AB82" s="1">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="AC82" s="1">
         <f>IF($AA82="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA82,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="83" spans="27:29">
       <c r="AA83" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),42),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),42),"")</f>
         <v/>
       </c>
       <c r="AB83" s="1">
@@ -9947,12 +9947,12 @@
       </c>
       <c r="AC83" s="1">
         <f>IF($AA83="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA83,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="84" spans="27:29">
       <c r="AA84" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),43),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),43),"")</f>
         <v/>
       </c>
       <c r="AB84" s="1">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="AC84" s="1">
         <f>IF($AA84="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA84,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="85" spans="27:29">
       <c r="AA85" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),44),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),44),"")</f>
         <v/>
       </c>
       <c r="AB85" s="1">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="AC85" s="1">
         <f>IF($AA85="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA85,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="86" spans="27:29">
       <c r="AA86" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),45),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),45),"")</f>
         <v/>
       </c>
       <c r="AB86" s="1">
@@ -9989,12 +9989,12 @@
       </c>
       <c r="AC86" s="1">
         <f>IF($AA86="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA86,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="87" spans="27:29">
       <c r="AA87" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),46),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),46),"")</f>
         <v/>
       </c>
       <c r="AB87" s="1">
@@ -10003,12 +10003,12 @@
       </c>
       <c r="AC87" s="1">
         <f>IF($AA87="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA87,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="88" spans="27:29">
       <c r="AA88" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),47),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),47),"")</f>
         <v/>
       </c>
       <c r="AB88" s="1">
@@ -10017,12 +10017,12 @@
       </c>
       <c r="AC88" s="1">
         <f>IF($AA88="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA88,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="89" spans="27:29">
       <c r="AA89" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),48),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),48),"")</f>
         <v/>
       </c>
       <c r="AB89" s="1">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="AC89" s="1">
         <f>IF($AA89="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA89,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="90" spans="27:29">
       <c r="AA90" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),49),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),49),"")</f>
         <v/>
       </c>
       <c r="AB90" s="1">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="AC90" s="1">
         <f>IF($AA90="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA90,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="91" spans="27:29">
       <c r="AA91" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),50),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),50),"")</f>
         <v/>
       </c>
       <c r="AB91" s="1">
@@ -10059,12 +10059,12 @@
       </c>
       <c r="AC91" s="1">
         <f>IF($AA91="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA91,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="92" spans="27:29">
       <c r="AA92" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),51),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),51),"")</f>
         <v/>
       </c>
       <c r="AB92" s="1">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="AC92" s="1">
         <f>IF($AA92="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA92,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="93" spans="27:29">
       <c r="AA93" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),52),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),52),"")</f>
         <v/>
       </c>
       <c r="AB93" s="1">
@@ -10087,12 +10087,12 @@
       </c>
       <c r="AC93" s="1">
         <f>IF($AA93="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA93,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="94" spans="27:29">
       <c r="AA94" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),53),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),53),"")</f>
         <v/>
       </c>
       <c r="AB94" s="1">
@@ -10101,12 +10101,12 @@
       </c>
       <c r="AC94" s="1">
         <f>IF($AA94="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA94,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="95" spans="27:29">
       <c r="AA95" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),54),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),54),"")</f>
         <v/>
       </c>
       <c r="AB95" s="1">
@@ -10115,12 +10115,12 @@
       </c>
       <c r="AC95" s="1">
         <f>IF($AA95="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA95,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="96" spans="27:29">
       <c r="AA96" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),55),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),55),"")</f>
         <v/>
       </c>
       <c r="AB96" s="1">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="AC96" s="1">
         <f>IF($AA96="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA96,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="97" spans="27:29">
       <c r="AA97" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),56),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),56),"")</f>
         <v/>
       </c>
       <c r="AB97" s="1">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="AC97" s="1">
         <f>IF($AA97="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA97,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="98" spans="27:29">
       <c r="AA98" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),57),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),57),"")</f>
         <v/>
       </c>
       <c r="AB98" s="1">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="AC98" s="1">
         <f>IF($AA98="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA98,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="99" spans="27:29">
       <c r="AA99" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),58),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),58),"")</f>
         <v/>
       </c>
       <c r="AB99" s="1">
@@ -10171,12 +10171,12 @@
       </c>
       <c r="AC99" s="1">
         <f>IF($AA99="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA99,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="100" spans="27:29">
       <c r="AA100" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),59),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),59),"")</f>
         <v/>
       </c>
       <c r="AB100" s="1">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AC100" s="1">
         <f>IF($AA100="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA100,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
     <row r="101" spans="27:29">
       <c r="AA101" s="1">
-        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/('💰 Payments'!$K$8:$K$67&gt;0),60),"")</f>
+        <f>IFERROR(AGGREGATE(15,6,'💰 Payments'!$L$8:$L$67/(('💰 Payments'!$L$8:$L$67&lt;&gt;"")*('💰 Payments'!$K$8:$K$67&gt;0)),60),"")</f>
         <v/>
       </c>
       <c r="AB101" s="1">
@@ -10199,11 +10199,10 @@
       </c>
       <c r="AC101" s="1">
         <f>IF($AA101="","",INDEX('💰 Payments'!$K$8:$K$67,MATCH($AA101,'💰 Payments'!$L$8:$L$67,0)))</f>
-        <v>0</v>
+        <v/>
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter>
@@ -11659,7 +11658,6 @@
       <c r="G79" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -11862,7 +11860,7 @@
       </c>
       <c r="G5" s="53"/>
       <c r="H5" s="83" t="str">
-        <f>"Overdue: "&amp;'_Data'!$AF$15&amp;" invoices"</f>
+        <f>"Overdue: "&amp;'_Data'!$AF$15&amp;IF('_Data'!$AF$15=1," invoice"," invoices")</f>
         <v>Overdue: 1 invoice</v>
       </c>
       <c r="I5" s="83"/>
@@ -13814,7 +13812,6 @@
       <c r="C98" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
@@ -15310,7 +15307,6 @@
       <c r="I68" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="28">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -16686,7 +16682,6 @@
       <c r="I53" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
@@ -17732,7 +17727,6 @@
       <c r="C48" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="26">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="B3:J3"/>
@@ -18759,7 +18753,6 @@
     <row r="47" spans="1:14" ht="18" customHeight="1"/>
     <row r="48" spans="1:14" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="28">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
@@ -19566,13 +19559,13 @@
       </c>
       <c r="J14" s="99">
         <f>'_Data'!$AF$10</f>
-        <v>4585</v>
+        <v>4584.615384615385</v>
       </c>
       <c r="K14" s="99"/>
       <c r="L14" s="99"/>
       <c r="M14" s="99">
         <f>'_Data'!$AF$12</f>
-        <v>1650</v>
+        <v>1650.0</v>
       </c>
       <c r="N14" s="99"/>
       <c r="O14" s="99"/>
@@ -20106,7 +20099,6 @@
       <c r="J86" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="51">
     <mergeCell ref="B2:M2"/>
     <mergeCell ref="B3:M3"/>
@@ -20249,7 +20241,7 @@
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="73" t="str">
-        <f>"Tax rate: "&amp;TEXT(TaxRate,"0.0%%")</f>
+        <f>"Tax rate: "&amp;TEXT(TaxRate,"0.0%")</f>
         <v>Tax rate: 5.0%</v>
       </c>
       <c r="E5" s="73"/>
@@ -20393,7 +20385,7 @@
     <row r="20" spans="1:8" ht="19" customHeight="1">
       <c r="A20" s="58"/>
       <c r="B20" s="58">
-        <f>IF($C20="","",ROW()-7)</f>
+        <f>IF($C20="","",ROW()-19)</f>
         <v>1</v>
       </c>
       <c r="C20" s="66">
@@ -20418,7 +20410,7 @@
     <row r="21" spans="1:8" ht="19" customHeight="1">
       <c r="A21" s="65"/>
       <c r="B21" s="65">
-        <f>IF($C21="","",ROW()-7)</f>
+        <f>IF($C21="","",ROW()-19)</f>
         <v>2</v>
       </c>
       <c r="C21" s="66">
@@ -20443,7 +20435,7 @@
     <row r="22" spans="1:8" ht="19" customHeight="1">
       <c r="A22" s="58"/>
       <c r="B22" s="58">
-        <f>IF($C22="","",ROW()-7)</f>
+        <f>IF($C22="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C22" s="14"/>
@@ -20455,7 +20447,7 @@
     <row r="23" spans="1:8" ht="19" customHeight="1">
       <c r="A23" s="65"/>
       <c r="B23" s="65">
-        <f>IF($C23="","",ROW()-7)</f>
+        <f>IF($C23="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C23" s="9"/>
@@ -20467,7 +20459,7 @@
     <row r="24" spans="1:8" ht="19" customHeight="1">
       <c r="A24" s="58"/>
       <c r="B24" s="58">
-        <f>IF($C24="","",ROW()-7)</f>
+        <f>IF($C24="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C24" s="14"/>
@@ -20479,7 +20471,7 @@
     <row r="25" spans="1:8" ht="19" customHeight="1">
       <c r="A25" s="65"/>
       <c r="B25" s="65">
-        <f>IF($C25="","",ROW()-7)</f>
+        <f>IF($C25="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C25" s="9"/>
@@ -20491,7 +20483,7 @@
     <row r="26" spans="1:8" ht="19" customHeight="1">
       <c r="A26" s="58"/>
       <c r="B26" s="58">
-        <f>IF($C26="","",ROW()-7)</f>
+        <f>IF($C26="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C26" s="14"/>
@@ -20503,7 +20495,7 @@
     <row r="27" spans="1:8" ht="19" customHeight="1">
       <c r="A27" s="65"/>
       <c r="B27" s="65">
-        <f>IF($C27="","",ROW()-7)</f>
+        <f>IF($C27="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C27" s="9"/>
@@ -20515,7 +20507,7 @@
     <row r="28" spans="1:8" ht="19" customHeight="1">
       <c r="A28" s="58"/>
       <c r="B28" s="58">
-        <f>IF($C28="","",ROW()-7)</f>
+        <f>IF($C28="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C28" s="14"/>
@@ -20527,7 +20519,7 @@
     <row r="29" spans="1:8" ht="19" customHeight="1">
       <c r="A29" s="65"/>
       <c r="B29" s="65">
-        <f>IF($C29="","",ROW()-7)</f>
+        <f>IF($C29="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C29" s="9"/>
@@ -20539,7 +20531,7 @@
     <row r="30" spans="1:8" ht="19" customHeight="1">
       <c r="A30" s="58"/>
       <c r="B30" s="58">
-        <f>IF($C30="","",ROW()-7)</f>
+        <f>IF($C30="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C30" s="14"/>
@@ -20551,7 +20543,7 @@
     <row r="31" spans="1:8" ht="19" customHeight="1">
       <c r="A31" s="65"/>
       <c r="B31" s="65">
-        <f>IF($C31="","",ROW()-7)</f>
+        <f>IF($C31="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C31" s="9"/>
@@ -20563,7 +20555,7 @@
     <row r="32" spans="1:8" ht="19" customHeight="1">
       <c r="A32" s="58"/>
       <c r="B32" s="58">
-        <f>IF($C32="","",ROW()-7)</f>
+        <f>IF($C32="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C32" s="14"/>
@@ -20575,7 +20567,7 @@
     <row r="33" spans="1:8" ht="19" customHeight="1">
       <c r="A33" s="65"/>
       <c r="B33" s="65">
-        <f>IF($C33="","",ROW()-7)</f>
+        <f>IF($C33="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C33" s="9"/>
@@ -20587,7 +20579,7 @@
     <row r="34" spans="1:8" ht="19" customHeight="1">
       <c r="A34" s="58"/>
       <c r="B34" s="58">
-        <f>IF($C34="","",ROW()-7)</f>
+        <f>IF($C34="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C34" s="14"/>
@@ -20599,7 +20591,7 @@
     <row r="35" spans="1:8" ht="19" customHeight="1">
       <c r="A35" s="65"/>
       <c r="B35" s="65">
-        <f>IF($C35="","",ROW()-7)</f>
+        <f>IF($C35="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C35" s="9"/>
@@ -20611,7 +20603,7 @@
     <row r="36" spans="1:8" ht="19" customHeight="1">
       <c r="A36" s="58"/>
       <c r="B36" s="58">
-        <f>IF($C36="","",ROW()-7)</f>
+        <f>IF($C36="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C36" s="14"/>
@@ -20623,7 +20615,7 @@
     <row r="37" spans="1:8" ht="19" customHeight="1">
       <c r="A37" s="65"/>
       <c r="B37" s="65">
-        <f>IF($C37="","",ROW()-7)</f>
+        <f>IF($C37="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C37" s="9"/>
@@ -20635,7 +20627,7 @@
     <row r="38" spans="1:8" ht="19" customHeight="1">
       <c r="A38" s="58"/>
       <c r="B38" s="58">
-        <f>IF($C38="","",ROW()-7)</f>
+        <f>IF($C38="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C38" s="14"/>
@@ -20647,7 +20639,7 @@
     <row r="39" spans="1:8" ht="19" customHeight="1">
       <c r="A39" s="65"/>
       <c r="B39" s="65">
-        <f>IF($C39="","",ROW()-7)</f>
+        <f>IF($C39="","",ROW()-19)</f>
         <v/>
       </c>
       <c r="C39" s="9"/>
@@ -20751,7 +20743,6 @@
     <row r="51" ht="19" customHeight="1"/>
     <row r="52" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="16">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
@@ -21683,7 +21674,6 @@
     <row r="67" ht="19" customHeight="1"/>
     <row r="68" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="75">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -21844,7 +21834,7 @@
         <v>284</v>
       </c>
       <c r="F4" s="66">
-        <v>46278</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="19" customHeight="1">
@@ -22015,8 +22005,8 @@
     </row>
     <row r="24" spans="2:8" ht="19" customHeight="1">
       <c r="D24" s="106" t="str">
-        <f>"Tax ("&amp;TEXT(TaxRate,"0.0%%")&amp;" - from Setup)"</f>
-        <v>Tax (0.0% - from Setup)</v>
+        <f>"Tax ("&amp;TEXT(TaxRate,"0.0%")&amp;" - from Setup)"</f>
+        <v>Tax (5.0% - from Setup)</v>
       </c>
       <c r="E24" s="106"/>
       <c r="F24" s="107">
@@ -22036,8 +22026,8 @@
     </row>
     <row r="26" spans="2:8" ht="19" customHeight="1">
       <c r="D26" s="106" t="str">
-        <f>"Deposit to confirm ("&amp;TEXT(DepositPct,"0%%")&amp;" - from Setup)"</f>
-        <v>Deposit to confirm (0% - from Setup)</v>
+        <f>"Deposit to confirm ("&amp;TEXT(DepositPct,"0%")&amp;" - from Setup)"</f>
+        <v>Deposit to confirm (40% - from Setup)</v>
       </c>
       <c r="E26" s="106"/>
       <c r="F26" s="107">
@@ -22201,7 +22191,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="24">
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="F2:H2"/>
@@ -22916,7 +22905,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="20">
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="G2:H2"/>
@@ -23685,7 +23673,6 @@
     <row r="95" ht="19" customHeight="1"/>
     <row r="96" ht="19" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="81">
     <mergeCell ref="B5:H7"/>
     <mergeCell ref="B8:H9"/>
@@ -23957,7 +23944,7 @@
     </row>
     <row r="9" spans="2:16" ht="30" customHeight="1">
       <c r="B9" s="40">
-        <f>COUNTIF('📅 Events'!$Q$8:$Q$47,"&lt;&gt;❌ Cancelled")+COUNTIF('📅 Events'!$Q$8:$Q$47,"❌ Cancelled")</f>
+        <f>SUMPRODUCT(('📅 Events'!$Q$8:$Q$47&lt;&gt;"")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled"))</f>
         <v>13</v>
       </c>
       <c r="C9" s="40"/>
@@ -24356,7 +24343,6 @@
     <row r="89" ht="18" customHeight="1"/>
     <row r="90" ht="18" customHeight="1"/>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="65">
     <mergeCell ref="B2:J2"/>
     <mergeCell ref="K2:P2"/>
@@ -25889,7 +25875,6 @@
       <c r="K57" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
@@ -26064,13 +26049,13 @@
     <row r="4" spans="2:18" ht="7" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="2:18" ht="26" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="50" t="str">
-        <f>"Bookings: "&amp;COUNTIF('📅 Events'!$Q$8:$Q$47,"&lt;&gt;❌ Cancelled")</f>
+        <f>"Bookings: "&amp;SUMPRODUCT(('📅 Events'!$Q$8:$Q$47&lt;&gt;"")*('📅 Events'!$Q$8:$Q$47&lt;&gt;"❌ Cancelled"))</f>
         <v>Bookings: 13</v>
       </c>
       <c r="C5" s="50"/>
       <c r="D5" s="73" t="str">
         <f>"In the pipeline: "&amp;COUNTIF('📅 Events'!$Q$8:$Q$47,"📝 Quote Sent") + COUNTIF('📅 Events'!$Q$8:$Q$47,"💰 Deposit Paid") + COUNTIF('📅 Events'!$Q$8:$Q$47,"✅ Confirmed") + COUNTIF('📅 Events'!$Q$8:$Q$47,"🎉 Completed")</f>
-        <v>In the pipeline: 13</v>
+        <v>In the pipeline: 12</v>
       </c>
       <c r="E5" s="73"/>
       <c r="F5" s="52" t="str">
@@ -27751,30 +27736,30 @@
       <c r="E48" s="71"/>
       <c r="F48" s="71"/>
       <c r="G48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$G$8:$G$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$G$8:$G$47)</f>
         <v>2005</v>
       </c>
       <c r="H48" s="71"/>
       <c r="I48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$I$8:$I$47)</f>
         <v>121</v>
       </c>
       <c r="J48" s="71"/>
       <c r="K48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$K$8:$K$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$K$8:$K$47)</f>
         <v>39130</v>
       </c>
       <c r="L48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$L$8:$L$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$L$8:$L$47)</f>
         <v>61100</v>
       </c>
       <c r="M48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$M$8:$M$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$M$8:$M$47)</f>
         <v>21970</v>
       </c>
       <c r="N48" s="71"/>
       <c r="O48" s="72">
-        <f>SUMPRODUCT(('📅 Events'!$E$8:$E$47&lt;&gt;"")*'📅 Events'!$O$8:$O$47)</f>
+        <f>SUMPRODUCT(--('📅 Events'!$E$8:$E$47&lt;&gt;""),'📅 Events'!$O$8:$O$47)</f>
         <v>18760</v>
       </c>
       <c r="P48" s="72">
@@ -27907,7 +27892,6 @@
       <c r="G57" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:O2"/>
     <mergeCell ref="B3:O3"/>
@@ -28277,7 +28261,7 @@
     <row r="23" spans="1:7" ht="21" customHeight="1"/>
     <row r="24" spans="1:7" ht="21" customHeight="1">
       <c r="B24" s="82" t="str">
-        <f>IF($E$16="","",Currency&amp;TEXT($E$16,"#,##0.00")&amp;"  for the event   ·   "&amp;Currency&amp;TEXT($E$17,"#,##0.00")&amp;" per guest")</f>
+        <f>IF($E$16="","",Currency&amp;TEXT($E$16,"#,##0.00")&amp;" for the event   ·   "&amp;Currency&amp;TEXT($E$17,"#,##0.00")&amp;" per guest")</f>
         <v>$4,400.00 for the event   ·   $36.67 per guest</v>
       </c>
       <c r="C24" s="82"/>
@@ -28435,7 +28419,6 @@
       <c r="C41" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B3:C3"/>
@@ -29593,7 +29576,6 @@
       <c r="I68" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
@@ -31108,7 +31090,6 @@
       <c r="I58" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="29">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>
@@ -31354,7 +31335,7 @@
         <v>12</v>
       </c>
       <c r="F8" s="88">
-        <f>IF($D8="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D8,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D8="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D8,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>15</v>
       </c>
       <c r="G8" s="88">
@@ -31365,7 +31346,7 @@
         <v>444</v>
       </c>
       <c r="I8" s="63">
-        <f>IF(OR($G8="",NOT(ISNUMBER($G8))),"",ROUND($G8*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D8,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G8="",NOT(ISNUMBER($G8))),"",ROUND($G8*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D8,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J8" s="89" t="s">
@@ -31393,7 +31374,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="88">
-        <f>IF($D9="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D9,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D9="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D9,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>2.8</v>
       </c>
       <c r="G9" s="88">
@@ -31404,7 +31385,7 @@
         <v>462</v>
       </c>
       <c r="I9" s="63">
-        <f>IF(OR($G9="",NOT(ISNUMBER($G9))),"",ROUND($G9*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D9,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G9="",NOT(ISNUMBER($G9))),"",ROUND($G9*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D9,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J9" s="90" t="s">
@@ -31430,7 +31411,7 @@
         <v>1.5</v>
       </c>
       <c r="F10" s="88">
-        <f>IF($D10="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D10,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D10="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D10,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>1.8</v>
       </c>
       <c r="G10" s="88">
@@ -31441,7 +31422,7 @@
         <v>467</v>
       </c>
       <c r="I10" s="63">
-        <f>IF(OR($G10="",NOT(ISNUMBER($G10))),"",ROUND($G10*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D10,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G10="",NOT(ISNUMBER($G10))),"",ROUND($G10*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D10,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J10" s="89"/>
@@ -31465,7 +31446,7 @@
         <v>10</v>
       </c>
       <c r="F11" s="88">
-        <f>IF($D11="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D11,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D11="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D11,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>18</v>
       </c>
       <c r="G11" s="88">
@@ -31476,7 +31457,7 @@
         <v>444</v>
       </c>
       <c r="I11" s="63">
-        <f>IF(OR($G11="",NOT(ISNUMBER($G11))),"",ROUND($G11*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D11,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G11="",NOT(ISNUMBER($G11))),"",ROUND($G11*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D11,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J11" s="90"/>
@@ -31498,7 +31479,7 @@
         <v>8</v>
       </c>
       <c r="F12" s="88">
-        <f>IF($D12="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D12,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D12="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D12,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>8</v>
       </c>
       <c r="G12" s="88">
@@ -31509,7 +31490,7 @@
         <v>467</v>
       </c>
       <c r="I12" s="63">
-        <f>IF(OR($G12="",NOT(ISNUMBER($G12))),"",ROUND($G12*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D12,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G12="",NOT(ISNUMBER($G12))),"",ROUND($G12*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D12,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J12" s="89"/>
@@ -31531,7 +31512,7 @@
         <v>6</v>
       </c>
       <c r="F13" s="88">
-        <f>IF($D13="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D13,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D13="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D13,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>14</v>
       </c>
       <c r="G13" s="88">
@@ -31542,7 +31523,7 @@
         <v>452</v>
       </c>
       <c r="I13" s="63">
-        <f>IF(OR($G13="",NOT(ISNUMBER($G13))),"",ROUND($G13*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D13,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G13="",NOT(ISNUMBER($G13))),"",ROUND($G13*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D13,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J13" s="90" t="s">
@@ -31568,7 +31549,7 @@
         <v>15</v>
       </c>
       <c r="F14" s="88">
-        <f>IF($D14="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D14,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D14="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D14,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>42</v>
       </c>
       <c r="G14" s="88">
@@ -31579,7 +31560,7 @@
         <v>441</v>
       </c>
       <c r="I14" s="63">
-        <f>IF(OR($G14="",NOT(ISNUMBER($G14))),"",ROUND($G14*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D14,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G14="",NOT(ISNUMBER($G14))),"",ROUND($G14*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D14,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J14" s="89"/>
@@ -31601,7 +31582,7 @@
         <v>30</v>
       </c>
       <c r="F15" s="88">
-        <f>IF($D15="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D15,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D15="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D15,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>15</v>
       </c>
       <c r="G15" s="88">
@@ -31612,7 +31593,7 @@
         <v>444</v>
       </c>
       <c r="I15" s="63">
-        <f>IF(OR($G15="",NOT(ISNUMBER($G15))),"",ROUND($G15*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D15,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G15="",NOT(ISNUMBER($G15))),"",ROUND($G15*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D15,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>180.0</v>
       </c>
       <c r="J15" s="90"/>
@@ -31636,7 +31617,7 @@
         <v>10</v>
       </c>
       <c r="F16" s="88">
-        <f>IF($D16="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D16,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D16="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D16,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>6</v>
       </c>
       <c r="G16" s="88">
@@ -31647,7 +31628,7 @@
         <v>444</v>
       </c>
       <c r="I16" s="63">
-        <f>IF(OR($G16="",NOT(ISNUMBER($G16))),"",ROUND($G16*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D16,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G16="",NOT(ISNUMBER($G16))),"",ROUND($G16*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D16,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>88.0</v>
       </c>
       <c r="J16" s="89"/>
@@ -31671,7 +31652,7 @@
         <v>4</v>
       </c>
       <c r="F17" s="88">
-        <f>IF($D17="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D17,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D17="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D17,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v>7</v>
       </c>
       <c r="G17" s="88">
@@ -31682,7 +31663,7 @@
         <v>452</v>
       </c>
       <c r="I17" s="63">
-        <f>IF(OR($G17="",NOT(ISNUMBER($G17))),"",ROUND($G17*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D17,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G17="",NOT(ISNUMBER($G17))),"",ROUND($G17*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D17,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v>0.0</v>
       </c>
       <c r="J17" s="90"/>
@@ -31698,7 +31679,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="85"/>
       <c r="F18" s="88">
-        <f>IF($D18="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D18,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D18="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D18,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G18" s="88">
@@ -31707,7 +31688,7 @@
       </c>
       <c r="H18" s="14"/>
       <c r="I18" s="63">
-        <f>IF(OR($G18="",NOT(ISNUMBER($G18))),"",ROUND($G18*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D18,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G18="",NOT(ISNUMBER($G18))),"",ROUND($G18*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D18,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J18" s="89"/>
@@ -31723,7 +31704,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="87"/>
       <c r="F19" s="88">
-        <f>IF($D19="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D19,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D19="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D19,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G19" s="88">
@@ -31732,7 +31713,7 @@
       </c>
       <c r="H19" s="9"/>
       <c r="I19" s="63">
-        <f>IF(OR($G19="",NOT(ISNUMBER($G19))),"",ROUND($G19*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D19,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G19="",NOT(ISNUMBER($G19))),"",ROUND($G19*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D19,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J19" s="90"/>
@@ -31748,7 +31729,7 @@
       <c r="D20" s="14"/>
       <c r="E20" s="85"/>
       <c r="F20" s="88">
-        <f>IF($D20="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D20,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D20="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D20,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G20" s="88">
@@ -31757,7 +31738,7 @@
       </c>
       <c r="H20" s="14"/>
       <c r="I20" s="63">
-        <f>IF(OR($G20="",NOT(ISNUMBER($G20))),"",ROUND($G20*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D20,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G20="",NOT(ISNUMBER($G20))),"",ROUND($G20*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D20,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J20" s="89"/>
@@ -31773,7 +31754,7 @@
       <c r="D21" s="9"/>
       <c r="E21" s="87"/>
       <c r="F21" s="88">
-        <f>IF($D21="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D21,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D21="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D21,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G21" s="88">
@@ -31782,7 +31763,7 @@
       </c>
       <c r="H21" s="9"/>
       <c r="I21" s="63">
-        <f>IF(OR($G21="",NOT(ISNUMBER($G21))),"",ROUND($G21*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D21,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G21="",NOT(ISNUMBER($G21))),"",ROUND($G21*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D21,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J21" s="90"/>
@@ -31798,7 +31779,7 @@
       <c r="D22" s="14"/>
       <c r="E22" s="85"/>
       <c r="F22" s="88">
-        <f>IF($D22="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D22,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D22="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D22,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G22" s="88">
@@ -31807,7 +31788,7 @@
       </c>
       <c r="H22" s="14"/>
       <c r="I22" s="63">
-        <f>IF(OR($G22="",NOT(ISNUMBER($G22))),"",ROUND($G22*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D22,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G22="",NOT(ISNUMBER($G22))),"",ROUND($G22*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D22,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J22" s="89"/>
@@ -31823,7 +31804,7 @@
       <c r="D23" s="9"/>
       <c r="E23" s="87"/>
       <c r="F23" s="88">
-        <f>IF($D23="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D23,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D23="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D23,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G23" s="88">
@@ -31832,7 +31813,7 @@
       </c>
       <c r="H23" s="9"/>
       <c r="I23" s="63">
-        <f>IF(OR($G23="",NOT(ISNUMBER($G23))),"",ROUND($G23*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D23,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G23="",NOT(ISNUMBER($G23))),"",ROUND($G23*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D23,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J23" s="90"/>
@@ -31848,7 +31829,7 @@
       <c r="D24" s="14"/>
       <c r="E24" s="85"/>
       <c r="F24" s="88">
-        <f>IF($D24="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D24,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D24="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D24,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G24" s="88">
@@ -31857,7 +31838,7 @@
       </c>
       <c r="H24" s="14"/>
       <c r="I24" s="63">
-        <f>IF(OR($G24="",NOT(ISNUMBER($G24))),"",ROUND($G24*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D24,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G24="",NOT(ISNUMBER($G24))),"",ROUND($G24*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D24,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J24" s="89"/>
@@ -31873,7 +31854,7 @@
       <c r="D25" s="9"/>
       <c r="E25" s="87"/>
       <c r="F25" s="88">
-        <f>IF($D25="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D25,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D25="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D25,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G25" s="88">
@@ -31882,7 +31863,7 @@
       </c>
       <c r="H25" s="9"/>
       <c r="I25" s="63">
-        <f>IF(OR($G25="",NOT(ISNUMBER($G25))),"",ROUND($G25*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D25,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G25="",NOT(ISNUMBER($G25))),"",ROUND($G25*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D25,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J25" s="90"/>
@@ -31898,7 +31879,7 @@
       <c r="D26" s="14"/>
       <c r="E26" s="85"/>
       <c r="F26" s="88">
-        <f>IF($D26="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D26,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D26="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D26,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G26" s="88">
@@ -31907,7 +31888,7 @@
       </c>
       <c r="H26" s="14"/>
       <c r="I26" s="63">
-        <f>IF(OR($G26="",NOT(ISNUMBER($G26))),"",ROUND($G26*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D26,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G26="",NOT(ISNUMBER($G26))),"",ROUND($G26*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D26,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J26" s="89"/>
@@ -31923,7 +31904,7 @@
       <c r="D27" s="9"/>
       <c r="E27" s="87"/>
       <c r="F27" s="88">
-        <f>IF($D27="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D27,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D27="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D27,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G27" s="88">
@@ -31932,7 +31913,7 @@
       </c>
       <c r="H27" s="9"/>
       <c r="I27" s="63">
-        <f>IF(OR($G27="",NOT(ISNUMBER($G27))),"",ROUND($G27*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D27,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G27="",NOT(ISNUMBER($G27))),"",ROUND($G27*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D27,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J27" s="90"/>
@@ -31948,7 +31929,7 @@
       <c r="D28" s="14"/>
       <c r="E28" s="85"/>
       <c r="F28" s="88">
-        <f>IF($D28="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D28,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D28="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D28,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G28" s="88">
@@ -31957,7 +31938,7 @@
       </c>
       <c r="H28" s="14"/>
       <c r="I28" s="63">
-        <f>IF(OR($G28="",NOT(ISNUMBER($G28))),"",ROUND($G28*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D28,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G28="",NOT(ISNUMBER($G28))),"",ROUND($G28*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D28,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J28" s="89"/>
@@ -31973,7 +31954,7 @@
       <c r="D29" s="9"/>
       <c r="E29" s="87"/>
       <c r="F29" s="88">
-        <f>IF($D29="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D29,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D29="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D29,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G29" s="88">
@@ -31982,7 +31963,7 @@
       </c>
       <c r="H29" s="9"/>
       <c r="I29" s="63">
-        <f>IF(OR($G29="",NOT(ISNUMBER($G29))),"",ROUND($G29*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D29,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G29="",NOT(ISNUMBER($G29))),"",ROUND($G29*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D29,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J29" s="90"/>
@@ -31998,7 +31979,7 @@
       <c r="D30" s="14"/>
       <c r="E30" s="85"/>
       <c r="F30" s="88">
-        <f>IF($D30="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D30,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D30="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D30,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G30" s="88">
@@ -32007,7 +31988,7 @@
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="63">
-        <f>IF(OR($G30="",NOT(ISNUMBER($G30))),"",ROUND($G30*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D30,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G30="",NOT(ISNUMBER($G30))),"",ROUND($G30*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D30,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J30" s="89"/>
@@ -32023,7 +32004,7 @@
       <c r="D31" s="9"/>
       <c r="E31" s="87"/>
       <c r="F31" s="88">
-        <f>IF($D31="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D31,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D31="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D31,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G31" s="88">
@@ -32032,7 +32013,7 @@
       </c>
       <c r="H31" s="9"/>
       <c r="I31" s="63">
-        <f>IF(OR($G31="",NOT(ISNUMBER($G31))),"",ROUND($G31*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D31,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G31="",NOT(ISNUMBER($G31))),"",ROUND($G31*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D31,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J31" s="90"/>
@@ -32048,7 +32029,7 @@
       <c r="D32" s="14"/>
       <c r="E32" s="85"/>
       <c r="F32" s="88">
-        <f>IF($D32="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D32,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D32="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D32,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G32" s="88">
@@ -32057,7 +32038,7 @@
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="63">
-        <f>IF(OR($G32="",NOT(ISNUMBER($G32))),"",ROUND($G32*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D32,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G32="",NOT(ISNUMBER($G32))),"",ROUND($G32*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D32,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J32" s="89"/>
@@ -32073,7 +32054,7 @@
       <c r="D33" s="9"/>
       <c r="E33" s="87"/>
       <c r="F33" s="88">
-        <f>IF($D33="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D33,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D33="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D33,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G33" s="88">
@@ -32082,7 +32063,7 @@
       </c>
       <c r="H33" s="9"/>
       <c r="I33" s="63">
-        <f>IF(OR($G33="",NOT(ISNUMBER($G33))),"",ROUND($G33*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D33,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G33="",NOT(ISNUMBER($G33))),"",ROUND($G33*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D33,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J33" s="90"/>
@@ -32098,7 +32079,7 @@
       <c r="D34" s="14"/>
       <c r="E34" s="85"/>
       <c r="F34" s="88">
-        <f>IF($D34="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D34,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D34="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D34,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G34" s="88">
@@ -32107,7 +32088,7 @@
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="63">
-        <f>IF(OR($G34="",NOT(ISNUMBER($G34))),"",ROUND($G34*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D34,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G34="",NOT(ISNUMBER($G34))),"",ROUND($G34*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D34,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J34" s="89"/>
@@ -32123,7 +32104,7 @@
       <c r="D35" s="9"/>
       <c r="E35" s="87"/>
       <c r="F35" s="88">
-        <f>IF($D35="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D35,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D35="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D35,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G35" s="88">
@@ -32132,7 +32113,7 @@
       </c>
       <c r="H35" s="9"/>
       <c r="I35" s="63">
-        <f>IF(OR($G35="",NOT(ISNUMBER($G35))),"",ROUND($G35*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D35,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G35="",NOT(ISNUMBER($G35))),"",ROUND($G35*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D35,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J35" s="90"/>
@@ -32148,7 +32129,7 @@
       <c r="D36" s="14"/>
       <c r="E36" s="85"/>
       <c r="F36" s="88">
-        <f>IF($D36="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D36,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D36="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D36,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G36" s="88">
@@ -32157,7 +32138,7 @@
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="63">
-        <f>IF(OR($G36="",NOT(ISNUMBER($G36))),"",ROUND($G36*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D36,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G36="",NOT(ISNUMBER($G36))),"",ROUND($G36*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D36,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J36" s="89"/>
@@ -32173,7 +32154,7 @@
       <c r="D37" s="9"/>
       <c r="E37" s="87"/>
       <c r="F37" s="88">
-        <f>IF($D37="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D37,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D37="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D37,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G37" s="88">
@@ -32182,7 +32163,7 @@
       </c>
       <c r="H37" s="9"/>
       <c r="I37" s="63">
-        <f>IF(OR($G37="",NOT(ISNUMBER($G37))),"",ROUND($G37*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D37,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G37="",NOT(ISNUMBER($G37))),"",ROUND($G37*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D37,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J37" s="90"/>
@@ -32198,7 +32179,7 @@
       <c r="D38" s="14"/>
       <c r="E38" s="85"/>
       <c r="F38" s="88">
-        <f>IF($D38="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D38,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D38="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D38,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G38" s="88">
@@ -32207,7 +32188,7 @@
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="63">
-        <f>IF(OR($G38="",NOT(ISNUMBER($G38))),"",ROUND($G38*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D38,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G38="",NOT(ISNUMBER($G38))),"",ROUND($G38*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D38,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J38" s="89"/>
@@ -32223,7 +32204,7 @@
       <c r="D39" s="9"/>
       <c r="E39" s="87"/>
       <c r="F39" s="88">
-        <f>IF($D39="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D39,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D39="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D39,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G39" s="88">
@@ -32232,7 +32213,7 @@
       </c>
       <c r="H39" s="9"/>
       <c r="I39" s="63">
-        <f>IF(OR($G39="",NOT(ISNUMBER($G39))),"",ROUND($G39*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D39,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G39="",NOT(ISNUMBER($G39))),"",ROUND($G39*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D39,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J39" s="90"/>
@@ -32248,7 +32229,7 @@
       <c r="D40" s="14"/>
       <c r="E40" s="85"/>
       <c r="F40" s="88">
-        <f>IF($D40="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D40,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D40="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D40,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G40" s="88">
@@ -32257,7 +32238,7 @@
       </c>
       <c r="H40" s="14"/>
       <c r="I40" s="63">
-        <f>IF(OR($G40="",NOT(ISNUMBER($G40))),"",ROUND($G40*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D40,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G40="",NOT(ISNUMBER($G40))),"",ROUND($G40*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D40,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J40" s="89"/>
@@ -32273,7 +32254,7 @@
       <c r="D41" s="9"/>
       <c r="E41" s="87"/>
       <c r="F41" s="88">
-        <f>IF($D41="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D41,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D41="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D41,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G41" s="88">
@@ -32282,7 +32263,7 @@
       </c>
       <c r="H41" s="9"/>
       <c r="I41" s="63">
-        <f>IF(OR($G41="",NOT(ISNUMBER($G41))),"",ROUND($G41*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D41,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G41="",NOT(ISNUMBER($G41))),"",ROUND($G41*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D41,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J41" s="90"/>
@@ -32298,7 +32279,7 @@
       <c r="D42" s="14"/>
       <c r="E42" s="85"/>
       <c r="F42" s="88">
-        <f>IF($D42="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D42,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D42="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D42,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G42" s="88">
@@ -32307,7 +32288,7 @@
       </c>
       <c r="H42" s="14"/>
       <c r="I42" s="63">
-        <f>IF(OR($G42="",NOT(ISNUMBER($G42))),"",ROUND($G42*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D42,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G42="",NOT(ISNUMBER($G42))),"",ROUND($G42*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D42,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J42" s="89"/>
@@ -32323,7 +32304,7 @@
       <c r="D43" s="9"/>
       <c r="E43" s="87"/>
       <c r="F43" s="88">
-        <f>IF($D43="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D43,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D43="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D43,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G43" s="88">
@@ -32332,7 +32313,7 @@
       </c>
       <c r="H43" s="9"/>
       <c r="I43" s="63">
-        <f>IF(OR($G43="",NOT(ISNUMBER($G43))),"",ROUND($G43*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D43,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G43="",NOT(ISNUMBER($G43))),"",ROUND($G43*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D43,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J43" s="90"/>
@@ -32348,7 +32329,7 @@
       <c r="D44" s="14"/>
       <c r="E44" s="85"/>
       <c r="F44" s="88">
-        <f>IF($D44="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D44,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D44="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D44,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G44" s="88">
@@ -32357,7 +32338,7 @@
       </c>
       <c r="H44" s="14"/>
       <c r="I44" s="63">
-        <f>IF(OR($G44="",NOT(ISNUMBER($G44))),"",ROUND($G44*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D44,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G44="",NOT(ISNUMBER($G44))),"",ROUND($G44*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D44,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J44" s="89"/>
@@ -32373,7 +32354,7 @@
       <c r="D45" s="9"/>
       <c r="E45" s="87"/>
       <c r="F45" s="88">
-        <f>IF($D45="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D45,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D45="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D45,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G45" s="88">
@@ -32382,7 +32363,7 @@
       </c>
       <c r="H45" s="9"/>
       <c r="I45" s="63">
-        <f>IF(OR($G45="",NOT(ISNUMBER($G45))),"",ROUND($G45*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D45,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G45="",NOT(ISNUMBER($G45))),"",ROUND($G45*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D45,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J45" s="90"/>
@@ -32398,7 +32379,7 @@
       <c r="D46" s="14"/>
       <c r="E46" s="85"/>
       <c r="F46" s="88">
-        <f>IF($D46="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D46,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D46="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D46,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G46" s="88">
@@ -32407,7 +32388,7 @@
       </c>
       <c r="H46" s="14"/>
       <c r="I46" s="63">
-        <f>IF(OR($G46="",NOT(ISNUMBER($G46))),"",ROUND($G46*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D46,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G46="",NOT(ISNUMBER($G46))),"",ROUND($G46*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D46,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J46" s="89"/>
@@ -32423,7 +32404,7 @@
       <c r="D47" s="9"/>
       <c r="E47" s="87"/>
       <c r="F47" s="88">
-        <f>IF($D47="","",IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D47,''📦 Inventory''!$F$8:$F$47),0))</f>
+        <f>IF($D47="","",IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D47,'📦 Inventory'!$F$8:$F$47),0))</f>
         <v/>
       </c>
       <c r="G47" s="88">
@@ -32432,7 +32413,7 @@
       </c>
       <c r="H47" s="9"/>
       <c r="I47" s="63">
-        <f>IF(OR($G47="",NOT(ISNUMBER($G47))),"",ROUND($G47*IFERROR(SUMIF(''📦 Inventory''!$C$8:$C$47,$D47,''📦 Inventory''!$H$8:$H$47),0),2))</f>
+        <f>IF(OR($G47="",NOT(ISNUMBER($G47))),"",ROUND($G47*IFERROR(SUMIF('📦 Inventory'!$C$8:$C$47,$D47,'📦 Inventory'!$H$8:$H$47),0),2))</f>
         <v/>
       </c>
       <c r="J47" s="90"/>
@@ -32450,7 +32431,7 @@
       <c r="G48" s="70"/>
       <c r="H48" s="71"/>
       <c r="I48" s="84">
-        <f>SUMPRODUCT(('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓")*('🛒 Shopping List'!$D$8:$D$47&lt;&gt;"")*'🛒 Shopping List'!$I$8:$I$47)</f>
+        <f>SUMPRODUCT(--(('🛒 Shopping List'!$J$8:$J$47&lt;&gt;"✓")*('🛒 Shopping List'!$D$8:$D$47&lt;&gt;"")),'🛒 Shopping List'!$I$8:$I$47)</f>
         <v>268.0</v>
       </c>
       <c r="J48" s="71"/>
@@ -32570,7 +32551,6 @@
       <c r="I58" s="24"/>
     </row>
   </sheetData>
-  <sheetProtection password="EC7C" sheet="1" formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0"/>
   <mergeCells count="28">
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="B3:I3"/>

--- a/products/Catering_Business_Manager_PREMIUM_Classic_EXAMPLE.xlsx
+++ b/products/Catering_Business_Manager_PREMIUM_Classic_EXAMPLE.xlsx
@@ -21753,7 +21753,7 @@
   </mergeCells>
   <conditionalFormatting sqref="B10:B58">
     <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
-      <formula>✓</formula>
+      <formula>"✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
@@ -22929,7 +22929,7 @@
   </mergeCells>
   <dataValidations count="8">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" promptTitle="Currency symbol" prompt="Pick a symbol, or type your own (e.g. Rs)." sqref="C9:D9">
-      <formula1>$,€,£,¥,₨,₹,A$,C$,R,kr,CHF</formula1>
+      <formula1>"$,€,£,¥,₨,₹,A$,C$,R,kr,CHF"</formula1>
     </dataValidation>
     <dataValidation type="decimal" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Pick a percentage" error="Enter a share of the price between 0% and 50%." sqref="C11:D11">
       <formula1>0</formula1>
